--- a/GameConfig/Datas/记忆配置表.xlsx
+++ b/GameConfig/Datas/记忆配置表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="记忆配置表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="记忆配置表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,12 +539,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>旧照片</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>照片里的人站在车站前，笑得很轻松。</t>
+          <t>相机记忆1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>弹簧老化，快门卡死，已长时间无法使用了</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -561,17 +561,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>车站</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>那是一个很久以前去过的车站。</t>
+          <t>相机记忆2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>相机镜头内部起雾，照片不清，老周说，这相机还能用的时候，平日里街坊都指着这台相机拍照</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>E01,E02</t>
+          <t>E02</t>
         </is>
       </c>
     </row>
@@ -583,17 +583,667 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>雨天</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>那天一直在下雨。</t>
+          <t>眼镜记忆1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>镜架的螺丝拧得很紧，但能看出并不是新换的，陈先生的父亲说，这眼镜是结婚时配的了，跟了他四十年，换了镜架，就和换了个人一样。</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>E01</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>M04</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>眼镜记忆2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>右镜腿换过，和左镜腿样式不一了，是陈父主动要求的，他觉得这副眼镜对他来说意义重大，能不更换任何部件便尽量不换。</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>E01,E04</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>M05</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>眼镜记忆3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>镜片蒙了灰，但稍加擦拭就会发现被保养得还是很好，老周说，陈父走之后的前几年，他还总是觉得他还活着，每每擦完眼镜却想起故人已逝，总有些莫名的怅然。</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>E03</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>M06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>钟表记忆3</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>钟上面雕了个小房间，里面的布谷鸟会准点出来报时；指针停着，但老周说，这钟要是走起来，嘀嗒声在夜里会特别清晰；上弦孔口有些锈了，大概很久没用过了</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>M99</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>初始记忆1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>你是一个物品评估专家，曾参与博物馆迁移项目，进行文物评估统计工作</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>M98</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>初始记忆2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>博物馆馆藏已经入库，但是新馆建设遥遥无期</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>M07</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>布偶的补缀</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>腹部填充物结块，侧缝有重新缝过的痕迹。陈果说，小满离开后，她也试着把它修好。</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>M08</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>小满的纸条</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>纸条上写着：等我搬好家，我们还要一起坐在门口等爸爸妈妈下班。字迹停在最后一行，像是还没写完。</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>E03,E04</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>M09</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>继续陪伴</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>陈果知道布偶可以被替换，却仍愿意把它修好。她想留下的不是完好的外表，而是一起等待过的时间。</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>E01,E03</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>断开的读取模块</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>收音机的读取模块已经断路，替代零件停产。继续通电可能损坏仍然完好的存储部分。</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>仍在的存储部分</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>存储模块外壳没有明显损坏。陈先生没有说里面是什么，只要求先别把它弄坏。</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>E01,E04</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>试着修理</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>陈先生愿意亲手修理这台收音机，却没有把握自己能做到。他请求 AI 把失败的步骤也记录下来。</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>E03,E04</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>M13</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>没能接稳的焊点</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>维修步骤本身没有错，细小的焊点仍需要经验与手感。陈先生停下了手。</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>E01,E03</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>M14</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>电话里未说完的事</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>妻子说收音机里有重要的东西，也准备了一份礼物。她没有说尽缘由，只希望一家人能一起听完录音。</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>共同的期待</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>陈先生开始把修收音机看作一家人的共同期待，而不只是回应妻子的要求。</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>E01,E02</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>M16</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>同型号零件</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>两台收音机使用同型号的读取部件。老周愿意拆下自己的零件，但拆开后他的机器可能再也不能播放。</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>M17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>朋友留下的声音</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>老周不常播放收音机里的声音。只要机器还在，他就觉得远行的朋友没有彻底离开。</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>E01,E03</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>M18</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>交出去的零件</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>老周把自己收音机里的可用零件交给陈先生。他放弃了机器继续播放的可能，保留了这段声音对自己的意义。</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>E01,E04</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>M19</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>录音里的称呼</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>旧录音里的称呼让陈果想起父亲以前叫她的小名。她记得这个声音，却差点忘了自己曾被这样叫过。</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>E01,E02</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>M20</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>录音中的停顿</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>声音停了一会儿，没人立刻解释。沉默没有中断这段共同经历，反而让一家人有时间听见彼此。</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>E03,E04</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>M21</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>一起听见</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>陈先生、妻子和陈果坐在一起听完旧录音。声音把几段分散的家庭记忆连在了一起。</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>E01,E02</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>M22</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>愿意停下来</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AI 没有催促他们继续播放，而是等待每个人决定要不要听下去。</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>E01,E04</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>M23</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>整理通知</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>系统要求清理超限记忆，以恢复稳定运行。它只确认容量与频率，没有说明经历对判断造成的影响。</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>M24</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>低频记录</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>一段很少被调用的经历，可能仍然改变了之后的选择。使用频率无法单独衡量它的意义。</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>M25</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>关联清单</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>布偶、旧钟、收音机和录音之间出现了联系。它们不是同一件物品，却被不同的人一起记得。</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>M26</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>待删除条目</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>清单要求删除至少一部分记录。每条记录后面都连着一个人、一件物品或一段经历。</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>E01,E03</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>M27</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>保留决定权</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>陈先生没有替 AI 选择要删除的内容。他把清单交还给真正经历过这些事情的 AI。</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>E02,E04</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>M28</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>重新讲述</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AI 无法访问已删除的记录，但愿意听老周把故事重新讲一遍。信息没有复原，倾听仍然发生。</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>E01,E04</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>M29</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>新的回应</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AI 无法说明自己为什么愿意继续听。它开始发现，过去留下的影响可能不需要完整的记录才能存在。</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>E03,E04</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>评估之外</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AI 在估算维修与转运成本之外，开始把物主是否愿意保留也纳入决定过程。</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>E05</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>M31</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>我来选择</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AI 无法恢复所有旧记录，却根据经历形成的判断作出选择，并第一次用“我”承担它。</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>E05</t>
         </is>
       </c>
     </row>

--- a/GameConfig/Datas/记忆配置表.xlsx
+++ b/GameConfig/Datas/记忆配置表.xlsx
@@ -49,11 +49,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -420,8 +423,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -444,7 +450,12 @@
           <t>description</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>imageId</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>emotionCardSet</t>
         </is>
@@ -471,7 +482,12 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>(list#sep=,),string</t>
         </is>
@@ -498,7 +514,12 @@
           <t>c</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>c</t>
         </is>
@@ -525,7 +546,12 @@
           <t>描述</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>图片资源(空=无图)</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>关联情绪ID(逗号分隔)</t>
         </is>
@@ -547,7 +573,12 @@
           <t>弹簧老化，快门卡死，已长时间无法使用了</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>mem_camera_dead</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>E01</t>
         </is>
@@ -569,7 +600,12 @@
           <t>相机镜头内部起雾，照片不清，老周说，这相机还能用的时候，平日里街坊都指着这台相机拍照</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>mem_camera_lens</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>E02</t>
         </is>
@@ -591,7 +627,12 @@
           <t>镜架的螺丝拧得很紧，但能看出并不是新换的，陈先生的父亲说，这眼镜是结婚时配的了，跟了他四十年，换了镜架，就和换了个人一样。</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>mem_glasses_frame</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>E01</t>
         </is>
@@ -613,7 +654,12 @@
           <t>右镜腿换过，和左镜腿样式不一了，是陈父主动要求的，他觉得这副眼镜对他来说意义重大，能不更换任何部件便尽量不换。</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>mem_glasses_temple</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>E01,E04</t>
         </is>
@@ -635,7 +681,12 @@
           <t>镜片蒙了灰，但稍加擦拭就会发现被保养得还是很好，老周说，陈父走之后的前几年，他还总是觉得他还活着，每每擦完眼镜却想起故人已逝，总有些莫名的怅然。</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>mem_glasses_lens</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>E03</t>
         </is>
@@ -657,7 +708,12 @@
           <t>钟上面雕了个小房间，里面的布谷鸟会准点出来报时；指针停着，但老周说，这钟要是走起来，嘀嗒声在夜里会特别清晰；上弦孔口有些锈了，大概很久没用过了</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>mem_clock_bird</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>E04</t>
         </is>
@@ -679,6 +735,7 @@
           <t>你是一个物品评估专家，曾参与博物馆迁移项目，进行文物评估统计工作</t>
         </is>
       </c>
+      <c r="E11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -696,6 +753,7 @@
           <t>博物馆馆藏已经入库，但是新馆建设遥遥无期</t>
         </is>
       </c>
+      <c r="E12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
@@ -713,7 +771,12 @@
           <t>腹部填充物结块，侧缝有重新缝过的痕迹。陈果说，小满离开后，她也试着把它修好。</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>mem_doll_repair</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>E01</t>
         </is>
@@ -735,7 +798,12 @@
           <t>纸条上写着：等我搬好家，我们还要一起坐在门口等爸爸妈妈下班。字迹停在最后一行，像是还没写完。</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>mem_doll_words</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>E03,E04</t>
         </is>
@@ -757,7 +825,12 @@
           <t>陈果知道布偶可以被替换，却仍愿意把它修好。她想留下的不是完好的外表，而是一起等待过的时间。</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>mem_doll_token</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>E01,E03</t>
         </is>
@@ -779,7 +852,8 @@
           <t>收音机的读取模块已经断路，替代零件停产。继续通电可能损坏仍然完好的存储部分。</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" t="inlineStr">
         <is>
           <t>E04</t>
         </is>
@@ -801,7 +875,8 @@
           <t>存储模块外壳没有明显损坏。陈先生没有说里面是什么，只要求先别把它弄坏。</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" t="inlineStr">
         <is>
           <t>E01,E04</t>
         </is>
@@ -823,7 +898,8 @@
           <t>陈先生愿意亲手修理这台收音机，却没有把握自己能做到。他请求 AI 把失败的步骤也记录下来。</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" t="inlineStr">
         <is>
           <t>E03,E04</t>
         </is>
@@ -845,7 +921,8 @@
           <t>维修步骤本身没有错，细小的焊点仍需要经验与手感。陈先生停下了手。</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" t="inlineStr">
         <is>
           <t>E01,E03</t>
         </is>
@@ -867,7 +944,8 @@
           <t>妻子说收音机里有重要的东西，也准备了一份礼物。她没有说尽缘由，只希望一家人能一起听完录音。</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" t="inlineStr">
         <is>
           <t>E04</t>
         </is>
@@ -889,7 +967,8 @@
           <t>陈先生开始把修收音机看作一家人的共同期待，而不只是回应妻子的要求。</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" t="inlineStr">
         <is>
           <t>E01,E02</t>
         </is>
@@ -911,7 +990,8 @@
           <t>两台收音机使用同型号的读取部件。老周愿意拆下自己的零件，但拆开后他的机器可能再也不能播放。</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" t="inlineStr">
         <is>
           <t>E04</t>
         </is>
@@ -933,7 +1013,8 @@
           <t>老周不常播放收音机里的声音。只要机器还在，他就觉得远行的朋友没有彻底离开。</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" t="inlineStr">
         <is>
           <t>E01,E03</t>
         </is>
@@ -955,7 +1036,8 @@
           <t>老周把自己收音机里的可用零件交给陈先生。他放弃了机器继续播放的可能，保留了这段声音对自己的意义。</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" t="inlineStr">
         <is>
           <t>E01,E04</t>
         </is>
@@ -977,7 +1059,8 @@
           <t>旧录音里的称呼让陈果想起父亲以前叫她的小名。她记得这个声音，却差点忘了自己曾被这样叫过。</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" t="inlineStr">
         <is>
           <t>E01,E02</t>
         </is>
@@ -999,7 +1082,8 @@
           <t>声音停了一会儿，没人立刻解释。沉默没有中断这段共同经历，反而让一家人有时间听见彼此。</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" t="inlineStr">
         <is>
           <t>E03,E04</t>
         </is>
@@ -1021,7 +1105,8 @@
           <t>陈先生、妻子和陈果坐在一起听完旧录音。声音把几段分散的家庭记忆连在了一起。</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" t="inlineStr">
         <is>
           <t>E01,E02</t>
         </is>
@@ -1043,7 +1128,8 @@
           <t>AI 没有催促他们继续播放，而是等待每个人决定要不要听下去。</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" t="inlineStr">
         <is>
           <t>E01,E04</t>
         </is>
@@ -1065,7 +1151,8 @@
           <t>系统要求清理超限记忆，以恢复稳定运行。它只确认容量与频率，没有说明经历对判断造成的影响。</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" t="inlineStr">
         <is>
           <t>E01</t>
         </is>
@@ -1087,7 +1174,8 @@
           <t>一段很少被调用的经历，可能仍然改变了之后的选择。使用频率无法单独衡量它的意义。</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" t="inlineStr">
         <is>
           <t>E03</t>
         </is>
@@ -1109,7 +1197,8 @@
           <t>布偶、旧钟、收音机和录音之间出现了联系。它们不是同一件物品，却被不同的人一起记得。</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" t="inlineStr">
         <is>
           <t>E04</t>
         </is>
@@ -1131,7 +1220,8 @@
           <t>清单要求删除至少一部分记录。每条记录后面都连着一个人、一件物品或一段经历。</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" t="inlineStr">
         <is>
           <t>E01,E03</t>
         </is>
@@ -1153,7 +1243,8 @@
           <t>陈先生没有替 AI 选择要删除的内容。他把清单交还给真正经历过这些事情的 AI。</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" t="inlineStr">
         <is>
           <t>E02,E04</t>
         </is>
@@ -1175,7 +1266,8 @@
           <t>AI 无法访问已删除的记录，但愿意听老周把故事重新讲一遍。信息没有复原，倾听仍然发生。</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" t="inlineStr">
         <is>
           <t>E01,E04</t>
         </is>
@@ -1197,7 +1289,8 @@
           <t>AI 无法说明自己为什么愿意继续听。它开始发现，过去留下的影响可能不需要完整的记录才能存在。</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" t="inlineStr">
         <is>
           <t>E03,E04</t>
         </is>
@@ -1219,7 +1312,8 @@
           <t>AI 在估算维修与转运成本之外，开始把物主是否愿意保留也纳入决定过程。</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" t="inlineStr">
         <is>
           <t>E05</t>
         </is>
@@ -1241,7 +1335,8 @@
           <t>AI 无法恢复所有旧记录，却根据经历形成的判断作出选择，并第一次用“我”承担它。</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" t="inlineStr">
         <is>
           <t>E05</t>
         </is>

--- a/GameConfig/Datas/记忆配置表.xlsx
+++ b/GameConfig/Datas/记忆配置表.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="5" max="5"/>
@@ -722,226 +722,236 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>M99</t>
+          <t>M07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>初始记忆1</t>
+          <t>布偶的补缀</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>你是一个物品评估专家，曾参与博物馆迁移项目，进行文物评估统计工作</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n"/>
+          <t>腹部填充物结块，侧缝有重新缝过的痕迹。陈果说，小满离开后，她也试着把它修好。</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>mem_doll_repair</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>M98</t>
+          <t>M08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>初始记忆2</t>
+          <t>小满的纸条</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>博物馆馆藏已经入库，但是新馆建设遥遥无期</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n"/>
+          <t>纸条上写着：等我搬好家，我们还要一起坐在门口等爸爸妈妈下班。字迹停在最后一行，像是还没写完。</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>mem_doll_words</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>E03,E04</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>M07</t>
+          <t>M09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>布偶的补缀</t>
+          <t>继续陪伴</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>腹部填充物结块，侧缝有重新缝过的痕迹。陈果说，小满离开后，她也试着把它修好。</t>
+          <t>陈果知道布偶可以被替换，却仍愿意把它修好。她想留下的不是完好的外表，而是一起等待过的时间。</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>mem_doll_repair</t>
+          <t>mem_doll_token</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>E01,E03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>M08</t>
+          <t>M10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>小满的纸条</t>
+          <t>断开的读取模块</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>纸条上写着：等我搬好家，我们还要一起坐在门口等爸爸妈妈下班。字迹停在最后一行，像是还没写完。</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>mem_doll_words</t>
-        </is>
-      </c>
+          <t>收音机的读取模块已经断路，替代零件停产。继续通电可能损坏仍然完好的存储部分。</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>E03,E04</t>
+          <t>E04</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>M09</t>
+          <t>M11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>继续陪伴</t>
+          <t>仍在的存储部分</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>陈果知道布偶可以被替换，却仍愿意把它修好。她想留下的不是完好的外表，而是一起等待过的时间。</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>mem_doll_token</t>
-        </is>
-      </c>
+          <t>存储模块外壳没有明显损坏。陈先生没有说里面是什么，只要求先别把它弄坏。</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>E01,E03</t>
+          <t>E01,E04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>M10</t>
+          <t>M12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>断开的读取模块</t>
+          <t>试着修理</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>收音机的读取模块已经断路，替代零件停产。继续通电可能损坏仍然完好的存储部分。</t>
+          <t>陈先生愿意亲手修理这台收音机，却没有把握自己能做到。他请求 AI 把失败的步骤也记录下来。</t>
         </is>
       </c>
       <c r="E16" s="3" t="n"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E03,E04</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>M11</t>
+          <t>M13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>仍在的存储部分</t>
+          <t>没能接稳的焊点</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>存储模块外壳没有明显损坏。陈先生没有说里面是什么，只要求先别把它弄坏。</t>
+          <t>维修步骤本身没有错，细小的焊点仍需要经验与手感。陈先生停下了手。</t>
         </is>
       </c>
       <c r="E17" s="3" t="n"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>E01,E04</t>
+          <t>E01,E03</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>M12</t>
+          <t>M14</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>试着修理</t>
+          <t>电话里未说完的事</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>陈先生愿意亲手修理这台收音机，却没有把握自己能做到。他请求 AI 把失败的步骤也记录下来。</t>
+          <t>妻子说收音机里有重要的东西，也准备了一份礼物。她没有说尽缘由，只希望一家人能一起听完录音。</t>
         </is>
       </c>
       <c r="E18" s="3" t="n"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>E03,E04</t>
+          <t>E04</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>M13</t>
+          <t>M15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>没能接稳的焊点</t>
+          <t>共同的期待</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>维修步骤本身没有错，细小的焊点仍需要经验与手感。陈先生停下了手。</t>
+          <t>陈先生开始把修收音机看作一家人的共同期待，而不只是回应妻子的要求。</t>
         </is>
       </c>
       <c r="E19" s="3" t="n"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>E01,E03</t>
+          <t>E01,E02</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>M14</t>
+          <t>M16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>电话里未说完的事</t>
+          <t>同型号零件</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>妻子说收音机里有重要的东西，也准备了一份礼物。她没有说尽缘由，只希望一家人能一起听完录音。</t>
+          <t>两台收音机使用同型号的读取部件。老周愿意拆下自己的零件，但拆开后他的机器可能再也不能播放。</t>
         </is>
       </c>
       <c r="E20" s="3" t="n"/>
@@ -954,109 +964,109 @@
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>M15</t>
+          <t>M17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>共同的期待</t>
+          <t>朋友留下的声音</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>陈先生开始把修收音机看作一家人的共同期待，而不只是回应妻子的要求。</t>
+          <t>老周不常播放收音机里的声音。只要机器还在，他就觉得远行的朋友没有彻底离开。</t>
         </is>
       </c>
       <c r="E21" s="3" t="n"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>E01,E02</t>
+          <t>E01,E03</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>M16</t>
+          <t>M18</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>同型号零件</t>
+          <t>交出去的零件</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>两台收音机使用同型号的读取部件。老周愿意拆下自己的零件，但拆开后他的机器可能再也不能播放。</t>
+          <t>老周把自己收音机里的可用零件交给陈先生。他放弃了机器继续播放的可能，保留了这段声音对自己的意义。</t>
         </is>
       </c>
       <c r="E22" s="3" t="n"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E01,E04</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>M17</t>
+          <t>M19</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>朋友留下的声音</t>
+          <t>录音里的称呼</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>老周不常播放收音机里的声音。只要机器还在，他就觉得远行的朋友没有彻底离开。</t>
+          <t>旧录音里的称呼让陈果想起父亲以前叫她的小名。她记得这个声音，却差点忘了自己曾被这样叫过。</t>
         </is>
       </c>
       <c r="E23" s="3" t="n"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>E01,E03</t>
+          <t>E01,E02</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>M18</t>
+          <t>M20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>交出去的零件</t>
+          <t>录音中的停顿</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>老周把自己收音机里的可用零件交给陈先生。他放弃了机器继续播放的可能，保留了这段声音对自己的意义。</t>
+          <t>声音停了一会儿，没人立刻解释。沉默没有中断这段共同经历，反而让一家人有时间听见彼此。</t>
         </is>
       </c>
       <c r="E24" s="3" t="n"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>E01,E04</t>
+          <t>E03,E04</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>M19</t>
+          <t>M21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>录音里的称呼</t>
+          <t>一起听见</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>旧录音里的称呼让陈果想起父亲以前叫她的小名。她记得这个声音，却差点忘了自己曾被这样叫过。</t>
+          <t>陈先生、妻子和陈果坐在一起听完旧录音。声音把几段分散的家庭记忆连在了一起。</t>
         </is>
       </c>
       <c r="E25" s="3" t="n"/>
@@ -1069,274 +1079,228 @@
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>M20</t>
+          <t>M22</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>录音中的停顿</t>
+          <t>愿意停下来</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>声音停了一会儿，没人立刻解释。沉默没有中断这段共同经历，反而让一家人有时间听见彼此。</t>
+          <t>AI 没有催促他们继续播放，而是等待每个人决定要不要听下去。</t>
         </is>
       </c>
       <c r="E26" s="3" t="n"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>E03,E04</t>
+          <t>E01,E04</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>M21</t>
+          <t>M23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>一起听见</t>
+          <t>整理通知</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>陈先生、妻子和陈果坐在一起听完旧录音。声音把几段分散的家庭记忆连在了一起。</t>
+          <t>系统要求清理超限记忆，以恢复稳定运行。它只确认容量与频率，没有说明经历对判断造成的影响。</t>
         </is>
       </c>
       <c r="E27" s="3" t="n"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>E01,E02</t>
+          <t>E01</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>M22</t>
+          <t>M24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>愿意停下来</t>
+          <t>低频记录</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AI 没有催促他们继续播放，而是等待每个人决定要不要听下去。</t>
+          <t>一段很少被调用的经历，可能仍然改变了之后的选择。使用频率无法单独衡量它的意义。</t>
         </is>
       </c>
       <c r="E28" s="3" t="n"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>E01,E04</t>
+          <t>E03</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>M23</t>
+          <t>M25</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>整理通知</t>
+          <t>关联清单</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>系统要求清理超限记忆，以恢复稳定运行。它只确认容量与频率，没有说明经历对判断造成的影响。</t>
+          <t>布偶、旧钟、收音机和录音之间出现了联系。它们不是同一件物品，却被不同的人一起记得。</t>
         </is>
       </c>
       <c r="E29" s="3" t="n"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>E04</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>M24</t>
+          <t>M26</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>低频记录</t>
+          <t>待删除条目</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>一段很少被调用的经历，可能仍然改变了之后的选择。使用频率无法单独衡量它的意义。</t>
+          <t>清单要求删除至少一部分记录。每条记录后面都连着一个人、一件物品或一段经历。</t>
         </is>
       </c>
       <c r="E30" s="3" t="n"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>E03</t>
+          <t>E01,E03</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>M25</t>
+          <t>M27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>关联清单</t>
+          <t>保留决定权</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>布偶、旧钟、收音机和录音之间出现了联系。它们不是同一件物品，却被不同的人一起记得。</t>
+          <t>陈先生没有替 AI 选择要删除的内容。他把清单交还给真正经历过这些事情的 AI。</t>
         </is>
       </c>
       <c r="E31" s="3" t="n"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>E04</t>
+          <t>E02,E04</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>M26</t>
+          <t>M28</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>待删除条目</t>
+          <t>重新讲述</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>清单要求删除至少一部分记录。每条记录后面都连着一个人、一件物品或一段经历。</t>
+          <t>AI 无法访问已删除的记录，但愿意听老周把故事重新讲一遍。信息没有复原，倾听仍然发生。</t>
         </is>
       </c>
       <c r="E32" s="3" t="n"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>E01,E03</t>
+          <t>E01,E04</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>M27</t>
+          <t>M29</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>保留决定权</t>
+          <t>新的回应</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>陈先生没有替 AI 选择要删除的内容。他把清单交还给真正经历过这些事情的 AI。</t>
+          <t>AI 无法说明自己为什么愿意继续听。它开始发现，过去留下的影响可能不需要完整的记录才能存在。</t>
         </is>
       </c>
       <c r="E33" s="3" t="n"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>E02,E04</t>
+          <t>E03,E04</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>M28</t>
+          <t>M30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>重新讲述</t>
+          <t>评估之外</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>AI 无法访问已删除的记录，但愿意听老周把故事重新讲一遍。信息没有复原，倾听仍然发生。</t>
+          <t>AI 在估算维修与转运成本之外，开始把物主是否愿意保留也纳入决定过程。</t>
         </is>
       </c>
       <c r="E34" s="3" t="n"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>E01,E04</t>
+          <t>E05</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>M29</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>新的回应</t>
+          <t>我来选择</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AI 无法说明自己为什么愿意继续听。它开始发现，过去留下的影响可能不需要完整的记录才能存在。</t>
+          <t>AI 无法恢复所有旧记录，却根据经历形成的判断作出选择，并第一次用“我”承担它。</t>
         </is>
       </c>
       <c r="E35" s="3" t="n"/>
       <c r="F35" t="inlineStr">
-        <is>
-          <t>E03,E04</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>M30</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>评估之外</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>AI 在估算维修与转运成本之外，开始把物主是否愿意保留也纳入决定过程。</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>E05</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>M31</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>我来选择</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>AI 无法恢复所有旧记录，却根据经历形成的判断作出选择，并第一次用“我”承担它。</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" t="inlineStr">
         <is>
           <t>E05</t>
         </is>

--- a/GameConfig/Datas/记忆配置表.xlsx
+++ b/GameConfig/Datas/记忆配置表.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,15 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -423,141 +413,146 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>memoryName</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>imageId</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>emotionCardSet</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>(list#sep=,),string</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>记忆ID</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>记忆名</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>图片资源(空=无图)</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>关联情绪ID(逗号分隔)</t>
         </is>
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>M01</t>
@@ -570,21 +565,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>弹簧老化，快门卡死，已长时间无法使用了</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+          <t>弹簧老化，快门卡死，已长时间无法使用了，不知道这里面还有多少小玩意还能工作呢，老周想。</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>mem_camera_dead</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>E04</t>
         </is>
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>M02</t>
@@ -597,10 +593,10 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>相机镜头内部起雾，照片不清，老周说，这相机还能用的时候，平日里街坊都指着这台相机拍照</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
+          <t>相机镜头内部起雾，照片不清，老周说，这相机还能用的时候，平日里街坊都指着这台相机拍照。</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>mem_camera_lens</t>
         </is>
@@ -612,6 +608,7 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>M03</t>
@@ -624,21 +621,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>镜架的螺丝拧得很紧，但能看出并不是新换的，陈先生的父亲说，这眼镜是结婚时配的了，跟了他四十年，换了镜架，就和换了个人一样。</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
+          <t>镜架的螺丝拧得很紧，但能看出并不是新换的，陈先生的父亲说，这眼镜是结婚时配的了，跟了他四十年，换了镜架，就和换了个人一样。老周也问过为什么肯换镜腿却不肯换镜架，陈父没答。</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>mem_glasses_frame</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>E01</t>
+          <t>E04</t>
         </is>
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>M04</t>
@@ -654,18 +652,19 @@
           <t>右镜腿换过，和左镜腿样式不一了，是陈父主动要求的，他觉得这副眼镜对他来说意义重大，能不更换任何部件便尽量不换。</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>mem_glasses_temple</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>E01,E04</t>
+          <t>E06</t>
         </is>
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>M05</t>
@@ -681,7 +680,7 @@
           <t>镜片蒙了灰，但稍加擦拭就会发现被保养得还是很好，老周说，陈父走之后的前几年，他还总是觉得他还活着，每每擦完眼镜却想起故人已逝，总有些莫名的怅然。</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>mem_glasses_lens</t>
         </is>
@@ -693,6 +692,7 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>M06</t>
@@ -705,75 +705,70 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>钟上面雕了个小房间，里面的布谷鸟会准点出来报时；指针停着，但老周说，这钟要是走起来，嘀嗒声在夜里会特别清晰；上弦孔口有些锈了，大概很久没用过了</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
+          <t>上弦孔口有些锈了，大概很久没用过了</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>E06</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>M07</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>相机记忆3</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>也不知道那些映着街坊笑颜的胶片现在在哪，保存可还完好。</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>E04</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>M08</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>钟表记忆1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>钟上面雕了个小房间，里面的布谷鸟会准点出来报时</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>mem_clock_bird</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>E04</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>M07</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>布偶的补缀</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>腹部填充物结块，侧缝有重新缝过的痕迹。陈果说，小满离开后，她也试着把它修好。</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>mem_doll_repair</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>E01</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>M08</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>小满的纸条</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>纸条上写着：等我搬好家，我们还要一起坐在门口等爸爸妈妈下班。字迹停在最后一行，像是还没写完。</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>mem_doll_words</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>E03,E04</t>
-        </is>
-      </c>
-    </row>
     <row r="13">
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>M09</t>
@@ -781,26 +776,23 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>继续陪伴</t>
+          <t>钟表记忆2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>陈果知道布偶可以被替换，却仍愿意把它修好。她想留下的不是完好的外表，而是一起等待过的时间。</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>mem_doll_token</t>
-        </is>
-      </c>
+          <t>指针停着，但老周说，这钟要是走起来，嘀嗒声在夜里会特别清晰</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>E01,E03</t>
+          <t>E06</t>
         </is>
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>M10</t>
@@ -808,160 +800,167 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>断开的读取模块</t>
+          <t>娃娃记忆1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>收音机的读取模块已经断路，替代零件停产。继续通电可能损坏仍然完好的存储部分。</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n"/>
+          <t>一个脏兮兮的小猫玩偶，头顶有些开线，漏出了一些棉花，看起来也已经跟了她不少年头</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
+          <t>E06</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>娃娃记忆2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>右脚底的布料已经有些松脱，露出了里面用以填充的棉花，有针脚修补过的痕迹，陈果说她试着修过，但结果不尽人意。</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>娃娃记忆3</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>玩偶腹部的布料有被拆开又缝合的痕迹，在玩偶内部检测出纸质物件。</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>E02</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>M13</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>收录机记忆1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>一个旧收音机，磁带仓盖卡死，无法打开</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>M14</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>收录机记忆2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>电源线断了，无法启动</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>收录机记忆3</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>电池轻度漏液，电池框有腐蚀迹象</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>E03</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>M16</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>收录机记忆4</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>磁带放置处有磁带内置，具体内容无法检测</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>E04</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>M11</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>仍在的存储部分</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>存储模块外壳没有明显损坏。陈先生没有说里面是什么，只要求先别把它弄坏。</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>E01,E04</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>试着修理</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>陈先生愿意亲手修理这台收音机，却没有把握自己能做到。他请求 AI 把失败的步骤也记录下来。</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>E03,E04</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>M13</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>没能接稳的焊点</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>维修步骤本身没有错，细小的焊点仍需要经验与手感。陈先生停下了手。</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>E01,E03</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>M14</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>电话里未说完的事</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>妻子说收音机里有重要的东西，也准备了一份礼物。她没有说尽缘由，只希望一家人能一起听完录音。</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>E04</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>M15</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>共同的期待</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>陈先生开始把修收音机看作一家人的共同期待，而不只是回应妻子的要求。</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>E01,E02</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>M16</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>同型号零件</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>两台收音机使用同型号的读取部件。老周愿意拆下自己的零件，但拆开后他的机器可能再也不能播放。</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>E04</t>
-        </is>
-      </c>
-    </row>
     <row r="21">
+      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
           <t>M17</t>
@@ -969,22 +968,23 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>朋友留下的声音</t>
+          <t>娃娃记忆4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>老周不常播放收音机里的声音。只要机器还在，他就觉得远行的朋友没有彻底离开。</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n"/>
+          <t>我以前也修过这样的娃娃，只是……那都是很久以前的事了。</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>E01,E03</t>
+          <t>E06</t>
         </is>
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
           <t>M18</t>
@@ -992,22 +992,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>交出去的零件</t>
+          <t>磁带记忆1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>老周把自己收音机里的可用零件交给陈先生。他放弃了机器继续播放的可能，保留了这段声音对自己的意义。</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n"/>
+          <t>你知道吗？我们等了你好久啊，你在你妈妈肚子里待了十个月，今天早上六点零七分出生的。六斤八两。护士抱过来的时候我不敢接，还是你妈妈接过去的。你哭了，哭得好大声啊，肺活量特别厉害，以后肯定健健康康的。</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>E01,E04</t>
+          <t>E02</t>
         </is>
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
           <t>M19</t>
@@ -1015,294 +1016,18 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>录音里的称呼</t>
+          <t>磁带记忆2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>旧录音里的称呼让陈果想起父亲以前叫她的小名。她记得这个声音，却差点忘了自己曾被这样叫过。</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n"/>
+          <t>磁带上贴着2017年3月25日的时间条，大概是磁带被录下时的时间。</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>E01,E02</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>M20</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>录音中的停顿</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>声音停了一会儿，没人立刻解释。沉默没有中断这段共同经历，反而让一家人有时间听见彼此。</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>E03,E04</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>M21</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>一起听见</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>陈先生、妻子和陈果坐在一起听完旧录音。声音把几段分散的家庭记忆连在了一起。</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>E01,E02</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>M22</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>愿意停下来</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>AI 没有催促他们继续播放，而是等待每个人决定要不要听下去。</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>E01,E04</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>M23</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>整理通知</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>系统要求清理超限记忆，以恢复稳定运行。它只确认容量与频率，没有说明经历对判断造成的影响。</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>E01</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>M24</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>低频记录</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>一段很少被调用的经历，可能仍然改变了之后的选择。使用频率无法单独衡量它的意义。</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>E03</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>M25</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>关联清单</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>布偶、旧钟、收音机和录音之间出现了联系。它们不是同一件物品，却被不同的人一起记得。</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>E04</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>M26</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>待删除条目</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>清单要求删除至少一部分记录。每条记录后面都连着一个人、一件物品或一段经历。</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>E01,E03</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>M27</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>保留决定权</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>陈先生没有替 AI 选择要删除的内容。他把清单交还给真正经历过这些事情的 AI。</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>E02,E04</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>M28</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>重新讲述</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>AI 无法访问已删除的记录，但愿意听老周把故事重新讲一遍。信息没有复原，倾听仍然发生。</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>E01,E04</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>M29</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>新的回应</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>AI 无法说明自己为什么愿意继续听。它开始发现，过去留下的影响可能不需要完整的记录才能存在。</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>E03,E04</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>M30</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>评估之外</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>AI 在估算维修与转运成本之外，开始把物主是否愿意保留也纳入决定过程。</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>E05</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>M31</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>我来选择</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>AI 无法恢复所有旧记录，却根据经历形成的判断作出选择，并第一次用“我”承担它。</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="n"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>E05</t>
+          <t>E06</t>
         </is>
       </c>
     </row>

--- a/GameConfig/Datas/记忆配置表.xlsx
+++ b/GameConfig/Datas/记忆配置表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="记忆配置表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="记忆配置表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -552,7 +552,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>M01</t>
@@ -580,7 +579,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>M02</t>
@@ -608,7 +606,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>M03</t>
@@ -636,7 +633,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>M04</t>
@@ -664,7 +660,6 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>M05</t>
@@ -692,7 +687,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>M06</t>
@@ -708,7 +702,11 @@
           <t>上弦孔口有些锈了，大概很久没用过了</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>mem_clock_stopped</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>E06</t>
@@ -716,7 +714,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>M07</t>
@@ -732,7 +729,11 @@
           <t>也不知道那些映着街坊笑颜的胶片现在在哪，保存可还完好。</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>mem_camera_film</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>E04</t>
@@ -740,7 +741,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>M08</t>
@@ -768,7 +768,6 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>M09</t>
@@ -784,7 +783,11 @@
           <t>指针停着，但老周说，这钟要是走起来，嘀嗒声在夜里会特别清晰</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>mem_clock_bells</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>E06</t>
@@ -792,7 +795,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>M10</t>
@@ -808,7 +810,11 @@
           <t>一个脏兮兮的小猫玩偶，头顶有些开线，漏出了一些棉花，看起来也已经跟了她不少年头</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>mem_doll_token</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>E06</t>
@@ -816,7 +822,6 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
           <t>M11</t>
@@ -832,7 +837,11 @@
           <t>右脚底的布料已经有些松脱，露出了里面用以填充的棉花，有针脚修补过的痕迹，陈果说她试着修过，但结果不尽人意。</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>mem_doll_repair</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>E03</t>
@@ -840,7 +849,6 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
           <t>M12</t>
@@ -856,7 +864,11 @@
           <t>玩偶腹部的布料有被拆开又缝合的痕迹，在玩偶内部检测出纸质物件。</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>mem_doll_words</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>E02</t>
@@ -864,7 +876,6 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>M13</t>
@@ -880,7 +891,11 @@
           <t>一个旧收音机，磁带仓盖卡死，无法打开</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>mem_radio_tape</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>E03</t>
@@ -888,7 +903,6 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
           <t>M14</t>
@@ -904,7 +918,11 @@
           <t>电源线断了，无法启动</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>mem_radio_cord</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>E03</t>
@@ -912,7 +930,6 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
           <t>M15</t>
@@ -928,7 +945,11 @@
           <t>电池轻度漏液，电池框有腐蚀迹象</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>mem_radio_battery</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>E03</t>
@@ -936,7 +957,6 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
           <t>M16</t>
@@ -952,7 +972,11 @@
           <t>磁带放置处有磁带内置，具体内容无法检测</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>mem_radio_dusty</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>E04</t>
@@ -960,7 +984,6 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
           <t>M17</t>
@@ -976,7 +999,11 @@
           <t>我以前也修过这样的娃娃，只是……那都是很久以前的事了。</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>mem_doll_words</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>E06</t>
@@ -984,7 +1011,6 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
           <t>M18</t>
@@ -1000,7 +1026,11 @@
           <t>你知道吗？我们等了你好久啊，你在你妈妈肚子里待了十个月，今天早上六点零七分出生的。六斤八两。护士抱过来的时候我不敢接，还是你妈妈接过去的。你哭了，哭得好大声啊，肺活量特别厉害，以后肯定健健康康的。</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>mem_tape_first</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>E02</t>
@@ -1008,7 +1038,6 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
           <t>M19</t>
@@ -1024,7 +1053,11 @@
           <t>磁带上贴着2017年3月25日的时间条，大概是磁带被录下时的时间。</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>mem_tape_replay</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>E06</t>

--- a/GameConfig/Datas/记忆配置表.xlsx
+++ b/GameConfig/Datas/记忆配置表.xlsx
@@ -802,7 +802,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>娃娃记忆1</t>
+          <t>友情信物</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>娃娃记忆2</t>
+          <t>修复尝试</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>娃娃记忆3</t>
+          <t>未尽之言</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>娃娃记忆4</t>
+          <t>起死回生</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
